--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21010445-0498-47CA-9B7C-D4205345C71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A9B949-9F46-4D9C-96E4-17DE4FF23E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 19-12-2025'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 29-01-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A9B949-9F46-4D9C-96E4-17DE4FF23E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE602ED-931B-485E-A7D8-C2F0724EFBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 29-01-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 02-02-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE602ED-931B-485E-A7D8-C2F0724EFBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03B9CE6-60BD-459F-A033-CB16F81E19DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 02-02-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 20-02-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03B9CE6-60BD-459F-A033-CB16F81E19DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967854C8-A927-475B-B476-85FACADBE3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 20-02-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 04-03-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967854C8-A927-475B-B476-85FACADBE3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F27839D-13AB-4AF2-9A23-9FC4D60CDC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 04-03-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 06-03-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F27839D-13AB-4AF2-9A23-9FC4D60CDC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC3FDA4-973A-4B54-9B2E-30964CB67F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC3FDA4-973A-4B54-9B2E-30964CB67F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4C7193-B51A-42DF-8EF4-8F25D0A23AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4C7193-B51A-42DF-8EF4-8F25D0A23AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D698B18A-7CBC-4EC9-8ED6-576E8CBF4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 06-03-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 09-03-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D698B18A-7CBC-4EC9-8ED6-576E8CBF4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5502CA06-A013-4649-947F-98D4BB691421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5502CA06-A013-4649-947F-98D4BB691421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A6C577-3176-4986-8ECE-380510390A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 09-03-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 11-03-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A6C577-3176-4986-8ECE-380510390A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B18243-EB19-4D7E-A59B-9C1964A5867A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B18243-EB19-4D7E-A59B-9C1964A5867A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4E1B89-A817-4A1A-9DE4-63B217F6A9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 11-03-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 20-03-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4E1B89-A817-4A1A-9DE4-63B217F6A9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5B979C-C921-4082-9A4D-028922D5CEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 20-03-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 25-03-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5B979C-C921-4082-9A4D-028922D5CEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1A81DA-3DAD-46DF-AE25-D869246C32C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 25-03-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 08-04-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1A81DA-3DAD-46DF-AE25-D869246C32C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9213507A-273A-4618-9C05-E5DB187722CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 08-04-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 10-04-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9213507A-273A-4618-9C05-E5DB187722CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC20EFD-C1F1-424A-AE9E-5FC206B1FCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC20EFD-C1F1-424A-AE9E-5FC206B1FCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2668DE20-FC95-4A5D-A5AB-2F7B03D9BFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 10-04-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 14-04-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2668DE20-FC95-4A5D-A5AB-2F7B03D9BFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DCE370-2BDA-4CD5-9BEE-A67B4F036C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 14-04-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 24-04-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DCE370-2BDA-4CD5-9BEE-A67B4F036C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F264598-ABEC-42CB-AC87-D1322A42E467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F264598-ABEC-42CB-AC87-D1322A42E467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7528F058-8A0B-4E91-90CC-B5D777930615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 24-04-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 27-04-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7528F058-8A0B-4E91-90CC-B5D777930615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1DB165-BF4D-4D09-A988-0CB31680F6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 27-04-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 06-05-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1DB165-BF4D-4D09-A988-0CB31680F6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E897904-320C-4FC4-BB59-C7105C9CBE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 06-05-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 01-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E897904-320C-4FC4-BB59-C7105C9CBE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126AE1CC-7A8C-4439-829C-4174B21B5EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 01-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 02-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126AE1CC-7A8C-4439-829C-4174B21B5EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2557D8-F6D5-45A7-8A84-C98D0A60C97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2557D8-F6D5-45A7-8A84-C98D0A60C97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C2DC21-14CA-4B5A-B125-C353BF9D00B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 02-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 05-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A9B949-9F46-4D9C-96E4-17DE4FF23E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEFFFB9-08CD-4007-A450-773B8ADE5222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D112240C-4287-452B-BAFF-3428C0CBB27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E829958-EFB5-4FA8-AB12-29FF56735BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E829958-EFB5-4FA8-AB12-29FF56735BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD71D091-0130-4009-B4D3-C9D413242158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD71D091-0130-4009-B4D3-C9D413242158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA15C29-1CB4-4068-8E1F-81E2B4456749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 09-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 15-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA15C29-1CB4-4068-8E1F-81E2B4456749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72409711-80B9-46D4-B4B9-C013B8202901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 15-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 22-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72409711-80B9-46D4-B4B9-C013B8202901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4202C2-FC29-4840-8D31-6156B9A4FC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 22-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 23-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4202C2-FC29-4840-8D31-6156B9A4FC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B1406A-3C5A-4CEE-8093-EBF1174E7530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72409711-80B9-46D4-B4B9-C013B8202901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E232EB-B2DB-447E-A805-755951C8F6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 22-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 23-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E232EB-B2DB-447E-A805-755951C8F6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15A4B26-7E17-49BA-8E9F-ABFDA1DA646D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 23-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 25-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15A4B26-7E17-49BA-8E9F-ABFDA1DA646D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A93973A-3E61-472E-B1F8-C97D78E6E40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 25-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 30-06-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A93973A-3E61-472E-B1F8-C97D78E6E40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8099060-73B1-4BD5-9F69-0EE03394EC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8099060-73B1-4BD5-9F69-0EE03394EC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301DBC7F-8197-4B87-856C-F62B2044C6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 30-06-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 01-07-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301DBC7F-8197-4B87-856C-F62B2044C6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5431C8-3EA7-43A8-AC0A-3E0A4FB0EA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 01-07-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 02-07-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301DBC7F-8197-4B87-856C-F62B2044C6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DB046C-B216-4FF4-B71F-237AFC3D6450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 01-07-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 03-07-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5431C8-3EA7-43A8-AC0A-3E0A4FB0EA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586A5A4D-812C-4D2E-8FB1-976341A0918C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 02-07-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 03-07-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586A5A4D-812C-4D2E-8FB1-976341A0918C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564377D8-6C23-47EB-B366-490C42081FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 03-07-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 09-07-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564377D8-6C23-47EB-B366-490C42081FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E166FCF-B847-4E31-AE56-785BC6505B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 09-07-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 19-08-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E166FCF-B847-4E31-AE56-785BC6505B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71560D28-ACDC-4C2E-8E52-EA12C5A4182E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 19-08-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 21-08-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71560D28-ACDC-4C2E-8E52-EA12C5A4182E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E014947-AE18-4859-B299-6263B96EF672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 21-08-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 27-08-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -534,7 +534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -582,7 +582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -596,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -610,7 +610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -627,7 +627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -661,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -675,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -720,7 +720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -734,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>33</v>
       </c>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E014947-AE18-4859-B299-6263B96EF672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE59192-F751-4E7C-BB22-F39BE762D153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 27-08-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 02-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE59192-F751-4E7C-BB22-F39BE762D153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DB8BB4-0ECE-460B-8B5C-AB08136E659E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 02-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 06-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DB8BB4-0ECE-460B-8B5C-AB08136E659E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B397C8C-67B4-41ED-90C4-8F0DAC8F8D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B397C8C-67B4-41ED-90C4-8F0DAC8F8D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610AF76C-B26F-4EBD-A914-904D38AFED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 06-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 07-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610AF76C-B26F-4EBD-A914-904D38AFED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F2E8A4-EEF4-4888-AF59-D30B432FB831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægevagtsystemer">'Opdateret d. 07-09-2026'!$A$1:$F$19</definedName>
+    <definedName name="Lægevagtsystemer">'Opdateret d. 09-09-2026'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægevagtsystemer_excel.XLSX
+++ b/html/Lægevagtsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F2E8A4-EEF4-4888-AF59-D30B432FB831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDBF688-E602-4F06-99C9-CD98AA7C6D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
